--- a/data/trans_orig/P57B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat) en 2023</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) en 2023 (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47566</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43964</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85271</t>
+          <t>84858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453290</t>
+          <t>452953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476822</t>
+          <t>476299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401397</t>
+          <t>400434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421059</t>
+          <t>420077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>860946</t>
+          <t>861359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890752</t>
+          <t>890433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49934</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29166</t>
+          <t>29799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48175</t>
+          <t>49222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399439</t>
+          <t>402959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425706</t>
+          <t>425264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330873</t>
+          <t>329826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349882</t>
+          <t>349249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738778</t>
+          <t>740733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769057</t>
+          <t>770317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598950</t>
+          <t>600816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651746</t>
+          <t>653189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131778</t>
+          <t>132580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146227</t>
+          <t>146436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>736518</t>
+          <t>735484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804229</t>
+          <t>802421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107730</t>
+          <t>105114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>144438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>44638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123224</t>
+          <t>121683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151694</t>
+          <t>140436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250480</t>
+          <t>253140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>875803</t>
+          <t>876679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913387</t>
+          <t>916003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>846312</t>
+          <t>847853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924229</t>
+          <t>924898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1740174</t>
+          <t>1737514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1838960</t>
+          <t>1850218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>63442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93783</t>
+          <t>93144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121737</t>
+          <t>120766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189306</t>
+          <t>189232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194218</t>
+          <t>193993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269162</t>
+          <t>269331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>370461</t>
+          <t>371100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399762</t>
+          <t>400802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>633728</t>
+          <t>633802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>701297</t>
+          <t>702268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1018116</t>
+          <t>1017947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093060</t>
+          <t>1093285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>22501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109337</t>
+          <t>109448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142358</t>
+          <t>142105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114301</t>
+          <t>116075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152454</t>
+          <t>156697</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212860</t>
+          <t>212188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230327</t>
+          <t>230713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595052</t>
+          <t>595305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>628073</t>
+          <t>627962</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>819645</t>
+          <t>815402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>857798</t>
+          <t>856024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>250625</t>
+          <t>240572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>358511</t>
+          <t>358255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>389877</t>
+          <t>382726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>525581</t>
+          <t>522009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>677829</t>
+          <t>682778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>860882</t>
+          <t>863400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2977778</t>
+          <t>2978034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3085664</t>
+          <t>3095717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2993257</t>
+          <t>2996829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3128961</t>
+          <t>3136112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5994244</t>
+          <t>5991726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6177297</t>
+          <t>6172348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68887</t>
+          <t>76451</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>62142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84858</t>
+          <t>96177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>466186</t>
+          <t>509537</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452953</t>
+          <t>495311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476299</t>
+          <t>519575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>411144</t>
+          <t>446076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400434</t>
+          <t>434107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420077</t>
+          <t>455380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>877330</t>
+          <t>955614</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861359</t>
+          <t>935888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890433</t>
+          <t>969923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>500856</t>
+          <t>545907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>500856</t>
+          <t>545907</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500856</t>
+          <t>545907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445361</t>
+          <t>486157</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445361</t>
+          <t>486157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445361</t>
+          <t>486157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>946217</t>
+          <t>1032065</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>946217</t>
+          <t>1032065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>946217</t>
+          <t>1032065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33334</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38049</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>31389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49222</t>
+          <t>52414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>76454</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58105</t>
+          <t>62674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>416039</t>
+          <t>445250</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402959</t>
+          <t>431306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425264</t>
+          <t>455525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>340999</t>
+          <t>378049</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329826</t>
+          <t>367202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349249</t>
+          <t>388227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>757039</t>
+          <t>823298</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740733</t>
+          <t>804857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770317</t>
+          <t>837078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>449373</t>
+          <t>480137</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>449373</t>
+          <t>480137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>449373</t>
+          <t>480137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>379048</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>379048</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379048</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>828422</t>
+          <t>899752</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>828422</t>
+          <t>899752</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>828422</t>
+          <t>899752</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>66599</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94973</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>627844</t>
+          <t>428753</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600816</t>
+          <t>415286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653189</t>
+          <t>439355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140204</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132580</t>
+          <t>150269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146436</t>
+          <t>165328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>768049</t>
+          <t>587636</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>735484</t>
+          <t>572441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>802421</t>
+          <t>599931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666008</t>
+          <t>469240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666008</t>
+          <t>469240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666008</t>
+          <t>469240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164449</t>
+          <t>184995</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164449</t>
+          <t>184995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164449</t>
+          <t>184995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>830457</t>
+          <t>654235</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>830457</t>
+          <t>654235</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>830457</t>
+          <t>654235</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>124196</t>
+          <t>135572</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105114</t>
+          <t>116026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144438</t>
+          <t>158355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91601</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121683</t>
+          <t>117820</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>215798</t>
+          <t>238022</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140436</t>
+          <t>216021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253140</t>
+          <t>267394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>896921</t>
+          <t>981352</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>876679</t>
+          <t>958569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916003</t>
+          <t>1000898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>877935</t>
+          <t>749597</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>847853</t>
+          <t>734227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924898</t>
+          <t>763905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1774856</t>
+          <t>1730949</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1737514</t>
+          <t>1701577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1850218</t>
+          <t>1752950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1021117</t>
+          <t>1116924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1021117</t>
+          <t>1116924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1021117</t>
+          <t>1116924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>969536</t>
+          <t>852047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>969536</t>
+          <t>852047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>969536</t>
+          <t>852047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1990654</t>
+          <t>1968971</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1990654</t>
+          <t>1968971</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1990654</t>
+          <t>1968971</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77632</t>
+          <t>92708</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63442</t>
+          <t>76042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93144</t>
+          <t>110478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>161851</t>
+          <t>180845</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120766</t>
+          <t>160501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189232</t>
+          <t>200328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>239483</t>
+          <t>273553</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193993</t>
+          <t>249473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269331</t>
+          <t>300979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>386612</t>
+          <t>460005</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371100</t>
+          <t>442235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400802</t>
+          <t>476671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>661183</t>
+          <t>628689</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>633802</t>
+          <t>609206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702268</t>
+          <t>649033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1047795</t>
+          <t>1088693</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>1061267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093285</t>
+          <t>1112773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>464244</t>
+          <t>552713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464244</t>
+          <t>552713</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>464244</t>
+          <t>552713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>823034</t>
+          <t>809534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>823034</t>
+          <t>809534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>823034</t>
+          <t>809534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1287278</t>
+          <t>1362246</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1287278</t>
+          <t>1362246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1287278</t>
+          <t>1362246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>124697</t>
+          <t>136478</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>119014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142105</t>
+          <t>154206</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>134230</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116075</t>
+          <t>127141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156697</t>
+          <t>166181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>225156</t>
+          <t>222749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212188</t>
+          <t>210017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230713</t>
+          <t>228178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>612713</t>
+          <t>683783</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595305</t>
+          <t>666055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>627962</t>
+          <t>701247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>837869</t>
+          <t>906532</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>815402</t>
+          <t>886084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>856024</t>
+          <t>925124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>234689</t>
+          <t>232004</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>234689</t>
+          <t>232004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>234689</t>
+          <t>232004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>737410</t>
+          <t>820261</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>737410</t>
+          <t>820261</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>737410</t>
+          <t>820261</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972099</t>
+          <t>1052265</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972099</t>
+          <t>1052265</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972099</t>
+          <t>1052265</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>317529</t>
+          <t>349278</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240572</t>
+          <t>315918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>358255</t>
+          <t>385998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>474660</t>
+          <t>527533</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>382726</t>
+          <t>491622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>522009</t>
+          <t>561072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>792189</t>
+          <t>876811</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>682778</t>
+          <t>826747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>863400</t>
+          <t>927314</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3018760</t>
+          <t>3047646</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2978034</t>
+          <t>3010926</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3095717</t>
+          <t>3081006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3044178</t>
+          <t>3045077</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2996829</t>
+          <t>3011538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3136112</t>
+          <t>3080988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6062937</t>
+          <t>6092723</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5991726</t>
+          <t>6042220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6172348</t>
+          <t>6142787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3336289</t>
+          <t>3396924</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3336289</t>
+          <t>3396924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3336289</t>
+          <t>3396924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3518838</t>
+          <t>3572610</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3518838</t>
+          <t>3572610</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3518838</t>
+          <t>3572610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6855126</t>
+          <t>6969534</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6855126</t>
+          <t>6969534</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6855126</t>
+          <t>6969534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
